--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T12:18:43+05:30</t>
+    <t>2026-05-16T12:58:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="183">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T12:58:39+05:30</t>
+    <t>2026-05-16T13:10:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -89,9 +89,9 @@
 workflow, and source-system-native semantic classifications and source system fidelity.
 Any coding system intended to represent an internal coding
 system SHALL follow the required naming convention:
-[customer]-[ehr]-[ResourceType]-[resource-subtype]-[element]-[source-specific-string]-InternalCode
+[customer]-[ehr]-[ResourceType]-[resource-subtype]-[element]-[SourceSpecificString]-InternalCode
 Example:
-acme-epic-Observation-lab-code-glucose-InternalCode</t>
+acme-epic-Observation-lab-code-Glucose-InternalCode</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -437,9 +437,6 @@
   </si>
   <si>
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>acme-epic-Observation-lab-code-Glucose-InternalCode</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -919,7 +916,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="45.109375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
@@ -1889,43 +1886,43 @@
         <v>20</v>
       </c>
       <c r="T9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -1940,21 +1937,21 @@
         <v>83</v>
       </c>
       <c r="AK9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AL9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AL9" t="s" s="2">
+      <c r="AM9" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>136</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1980,13 +1977,13 @@
         <v>89</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2036,7 +2033,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2051,21 +2048,21 @@
         <v>83</v>
       </c>
       <c r="AK10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AL10" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="AL10" t="s" s="2">
+      <c r="AM10" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>145</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2088,17 +2085,17 @@
         <v>106</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2147,7 +2144,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -2162,21 +2159,21 @@
         <v>83</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AL11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>155</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2202,14 +2199,14 @@
         <v>89</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -2258,7 +2255,7 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2273,21 +2270,21 @@
         <v>83</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>164</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2310,19 +2307,19 @@
         <v>106</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -2371,7 +2368,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2386,21 +2383,21 @@
         <v>83</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>175</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2426,16 +2423,16 @@
         <v>89</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -2484,7 +2481,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2499,13 +2496,13 @@
         <v>83</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T13:10:22+05:30</t>
+    <t>2026-05-16T16:45:26+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T16:45:26+05:30</t>
+    <t>2026-05-17T00:25:02+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-17T00:25:02+05:30</t>
+    <t>2026-05-19T06:46:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T06:46:39+05:30</t>
+    <t>2026-05-19T11:54:54+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="184">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T11:54:54+05:30</t>
+    <t>2026-05-25T12:07:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -389,10 +389,6 @@
     <t>internalCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
     <t>Customer-specific internal coding with required internal code system format</t>
   </si>
   <si>
@@ -439,9 +435,21 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>acme-epic-Observation-lab-code-Glucose-InternalCode</t>
+  </si>
+  <si>
     <t>Coding.system</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+coding314e-3:Internal coding systems SHALL follow the format:
+[customer]-[ehr]-[ResourceType]-[resource-subtype]-[eleMent]-[SourceSpecificString]-InternalCode
+Example:
+acme-epic-Observation-lab-code-Glucose-InternalCode {coding.where(system.exists())
+  .where(system.endsWith('-InternalCode'))
+  .all(system.matches('^[^-]+-[^-]+-[^-]+-[^-]+-[^-]+-[^-]+-InternalCode$'))}</t>
+  </si>
+  <si>
     <t>C*E.3</t>
   </si>
   <si>
@@ -457,10 +465,12 @@
     <t>CodeableConcept.coding.version</t>
   </si>
   <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+    <t>Version of the system</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing
+this code.
+The interpretation of version is defined by the code system.</t>
   </si>
   <si>
     <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
@@ -549,7 +559,8 @@
     <t>If this coding was chosen directly by the user</t>
   </si>
   <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+    <t>Indicates that this coding was chosen by a user directly
+rather than generated automatically.</t>
   </si>
   <si>
     <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
@@ -916,7 +927,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="45.109375" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
@@ -1528,13 +1539,13 @@
         <v>106</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="N6" t="s" s="2">
         <v>110</v>
@@ -1615,10 +1626,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1724,10 +1735,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1835,10 +1846,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1861,19 +1872,19 @@
         <v>106</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="N9" t="s" s="2">
+      <c r="O9" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="O9" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="P9" t="s" s="2">
         <v>20</v>
@@ -1886,7 +1897,7 @@
         <v>20</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="U9" t="s" s="2">
         <v>20</v>
@@ -1934,24 +1945,24 @@
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1977,13 +1988,13 @@
         <v>89</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2033,7 +2044,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2048,21 +2059,21 @@
         <v>83</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2085,17 +2096,17 @@
         <v>106</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2144,7 +2155,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -2159,21 +2170,21 @@
         <v>83</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2199,14 +2210,14 @@
         <v>89</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -2255,7 +2266,7 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2270,21 +2281,21 @@
         <v>83</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2307,19 +2318,19 @@
         <v>106</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -2368,7 +2379,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2383,21 +2394,21 @@
         <v>83</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2423,16 +2434,16 @@
         <v>89</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -2481,7 +2492,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2496,13 +2507,13 @@
         <v>83</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:07:44+05:30</t>
+    <t>2026-05-25T12:34:12+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:34:12+05:30</t>
+    <t>2026-05-25T13:52:53+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T13:52:53+05:30</t>
+    <t>2026-05-25T14:14:21+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:14:21+05:30</t>
+    <t>2026-05-25T14:26:28+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:26:28+05:30</t>
+    <t>2026-05-25T14:41:34+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:41:34+05:30</t>
+    <t>2026-05-25T15:12:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:12:42+05:30</t>
+    <t>2026-05-25T15:24:41+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:24:41+05:30</t>
+    <t>2026-05-25T15:48:57+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:48:57+05:30</t>
+    <t>2026-05-25T16:36:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T16:36:06+05:30</t>
+    <t>2026-05-26T08:48:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T08:48:22+05:30</t>
+    <t>2026-05-26T12:06:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T19:54:55+05:30</t>
+    <t>2026-06-10T16:33:40+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-codeableconcept-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
